--- a/data/templates/eval-report.xlsx
+++ b/data/templates/eval-report.xlsx
@@ -2582,9 +2582,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="82.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>57</v>
-      </c>
+      <c r="A1" s="3"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
@@ -2605,9 +2603,9 @@
       <c r="H2" s="4"/>
       <c r="I2" s="49"/>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1</v>
+        <v>76</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -2618,9 +2616,9 @@
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>2</v>
+        <v>77</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2631,8 +2629,18 @@
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
     </row>
-    <row r="5" s="1" customFormat="true" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I5" s="49"/>
+    <row r="5" s="1" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
     </row>
     <row r="6" s="1" customFormat="true" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I6" s="49"/>
